--- a/再申請_不備修正_2026-09-11/02_減価償却費の整合/減価償却費_突合表.xlsx
+++ b/再申請_不備修正_2026-09-11/02_減価償却費の整合/減価償却費_突合表.xlsx
@@ -33,7 +33,23 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">申請システムの「直近の決算年月」と決算書の事業年度末を一致させる。例示値。</t>
+          <t xml:space="preserve">株式会社</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">JTC </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">決算書（損益計算書）の事業年度。</t>
         </r>
       </text>
     </comment>
@@ -45,7 +61,55 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">不備指摘を受けた時点で申請システムに入っている値。例示値（千円丸めの典型例）。</t>
+          <t xml:space="preserve">不備指摘時点の入力値。事業計画書（その</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">）参考書式シート </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">E33 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">および算定根拠の記載より。決算書より</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">円少ない。</t>
         </r>
       </text>
     </comment>
@@ -160,7 +224,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026</t>
+      <t xml:space="preserve">2025</t>
     </r>
     <r>
       <rPr>
@@ -179,356 +243,651 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月期（自 令和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日 至 令和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">申請システムの現在の入力値（③減価償却費）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資料名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">科目名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金額（円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">決算書の該当ページ・行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">備考（マーカー・補記の内容）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">損益計算書（販売費及び一般管理費）→ 販売費及び一般管理費 明細</t>
+  </si>
+  <si>
+    <t xml:space="preserve">減価償却費</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決算書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDF 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ページ目 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">黄色マーカー＋補記「③減価償却費 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22,704,796</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円」（提出版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に反映済み）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">製造原価報告書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成なし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上原価は期首棚卸＋仕入－期末棚卸のみで製造原価報告書を作成していないため該当なし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">個別注記表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（減価償却の方法の注記のみ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決算書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDF 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ページ目</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">金額の記載なし。提出書類には含める。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">損益計算書 販管費</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リース料 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12,531,217</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決算書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDF 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ページ目</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">費用処理のリース料は減価償却費ではないため合算しない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予備行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合計（申請システムに入力する値）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">この値を</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円単位で「③減価償却費」に入力する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">差額（合計 − 現在の入力値）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">になれば整合済み</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">判定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参考（合算しない項目）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">減価償却累計額（今回の注記表には記載なし）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計額は費用ではないため③減価償却費に含めない。提出書類には含める。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">補記例（損益計算書</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ページ目余白に記載）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出典</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">株式会社</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JTC </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">損益計算書・販売費及び一般管理費・個別注記表（自 令和</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日 至 令和</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">31</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日）。申請システム現在値は事業計画書（その</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月期</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">申請システムの現在の入力値（③減価償却費）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">資料名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">科目名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金額（円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">決算書の該当ページ・行</t>
-  </si>
-  <si>
-    <t xml:space="preserve">備考（マーカー・補記の内容）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">損益計算書（販売費及び一般管理費）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">減価償却費</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">販管費</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黄色マーカー＋補記「③減価償却費 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,234,567</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円」</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">製造原価報告書（経費）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">経費</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">黄色マーカー＋補記「③減価償却費 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">890,123</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円」</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">販売費及び一般管理費明細</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">損益計算書の内訳の場合は二重計上しないよう金額欄は空欄にし、備考に「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">No.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の内訳」と記載</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">損益計算書 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">製造原価報告書</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">無形固定資産償却（ソフトウェア償却等）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手引きの③減価償却費の定義に含まれる場合のみ入力</t>
-  </si>
-  <si>
-    <t xml:space="preserve">リース資産減価償却費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予備行</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合計（申請システムに入力する値）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">この値を</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円単位で「③減価償却費」に入力する</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">差額（合計 − 現在の入力値）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">になれば整合済み</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参考（合算しない項目）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">個別注記表</t>
-  </si>
-  <si>
-    <t xml:space="preserve">減価償却累計額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">累計額は費用ではないため③減価償却費に含めない。提出書類には含める。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">補記例（損益計算書</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ページ目余白に記載）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出典</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">金額はすべて自社の決算書（直近の決算年月）から転記する。例示値は形式を示すためのもので、実数値に置き換えること。</t>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）より。</t>
     </r>
   </si>
 </sst>
@@ -540,7 +899,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,6 +983,11 @@
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -694,7 +1058,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -732,10 +1096,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1060,7 +1420,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1234000</v>
+        <v>22704793</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1094,9 +1454,9 @@
         <v>12</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1234567</v>
-      </c>
-      <c r="E8" s="10" t="s">
+        <v>22704796</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="9" t="s">
@@ -1113,10 +1473,8 @@
       <c r="C9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>890123</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="5"/>
+      <c r="E9" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="9" t="s">
@@ -1131,12 +1489,14 @@
         <v>18</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" s="5"/>
-      <c r="E10" s="10"/>
+      <c r="E10" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="F10" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1144,88 +1504,86 @@
         <v>4</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="F11" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>23</v>
-      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="10"/>
+      <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="10"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="10"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12" t="n">
+      <c r="B15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11" t="n">
         <f aca="false">SUM(D8:D14)</f>
-        <v>2124690</v>
-      </c>
-      <c r="E15" s="11"/>
+        <v>22704796</v>
+      </c>
+      <c r="E15" s="10"/>
       <c r="F15" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <f aca="false">D15-C5</f>
-        <v>890690</v>
+        <v>3</v>
       </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="14" t="s">
-        <v>29</v>
+      <c r="F16" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="3" t="str">
@@ -1236,44 +1594,44 @@
       <c r="F17" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="B19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="B20" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="18" t="str">
-        <f aca="false">"③減価償却費 = "&amp;TEXT(D8,"#,##0")&amp;"円（販管費）＋ "&amp;TEXT(D9,"#,##0")&amp;"円（製造原価）＝ "&amp;TEXT(D15,"#,##0")&amp;"円"</f>
-        <v>③減価償却費 = 1,234,567円（販管費）＋ 890,123円（製造原価）＝ 2,124,690円</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="B23" s="17" t="str">
+        <f aca="false">"③減価償却費 = 販売費及び一般管理費 減価償却費 "&amp;TEXT(D8,"#,##0")&amp;"円（製造原価報告書 作成なし）＝ "&amp;TEXT(D15,"#,##0")&amp;"円"</f>
+        <v>③減価償却費 = 販売費及び一般管理費 減価償却費 22,704,796円（製造原価報告書 作成なし）＝ 22,704,796円</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>36</v>
       </c>
     </row>
